--- a/data/trans_bre/P19-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 10,61</t>
+          <t>-3,63; 10,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 9,02</t>
+          <t>-5,95; 9,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 12,82</t>
+          <t>-3,77; 11,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 10,96</t>
+          <t>-6,0; 10,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 64,94</t>
+          <t>-15,96; 61,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 39,84</t>
+          <t>-20,85; 44,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 49,81</t>
+          <t>-11,52; 44,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 35,3</t>
+          <t>-13,84; 32,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 12,26</t>
+          <t>0,67; 12,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 6,37</t>
+          <t>-4,83; 5,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 9,63</t>
+          <t>-1,81; 9,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 8,35</t>
+          <t>-3,61; 8,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 46,59</t>
+          <t>1,88; 46,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 28,26</t>
+          <t>-17,82; 27,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 37,06</t>
+          <t>-5,91; 37,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 40,23</t>
+          <t>-12,45; 44,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 12,93</t>
+          <t>-0,5; 12,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 19,89</t>
+          <t>4,82; 19,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 8,1</t>
+          <t>-6,11; 8,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 15,91</t>
+          <t>3,48; 15,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 69,26</t>
+          <t>-3,36; 63,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,4; 102,78</t>
+          <t>17,99; 95,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 30,37</t>
+          <t>-18,37; 31,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 92,99</t>
+          <t>12,33; 87,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 12,79</t>
+          <t>-0,5; 12,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 5,58</t>
+          <t>-7,67; 5,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 13,77</t>
+          <t>0,21; 14,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 16,33</t>
+          <t>-15,16; 15,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 55,37</t>
+          <t>-2,18; 56,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 23,68</t>
+          <t>-25,3; 21,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 51,43</t>
+          <t>0,58; 55,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 46,15</t>
+          <t>-33,25; 44,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 4,71</t>
+          <t>-14,68; 3,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 22,49</t>
+          <t>5,11; 21,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 16,85</t>
+          <t>1,53; 16,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 11,43</t>
+          <t>0,27; 11,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 15,25</t>
+          <t>-37,53; 13,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,96; 147,37</t>
+          <t>21,15; 146,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 136,22</t>
+          <t>6,98; 135,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 125,58</t>
+          <t>1,55; 124,74</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,67; 22,27</t>
+          <t>6,99; 21,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 7,64</t>
+          <t>-8,41; 7,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 12,88</t>
+          <t>-3,03; 13,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 10,91</t>
+          <t>-2,68; 11,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,39; 136,64</t>
+          <t>30,67; 132,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 29,22</t>
+          <t>-23,99; 30,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 39,4</t>
+          <t>-7,32; 43,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 54,64</t>
+          <t>-10,13; 53,44</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,48</t>
+          <t>3,94; 14,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 13,84</t>
+          <t>4,12; 14,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 14,35</t>
+          <t>3,51; 14,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 6,94</t>
+          <t>-20,21; 6,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 53,38</t>
+          <t>12,46; 56,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,96; 63,21</t>
+          <t>15,56; 65,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,66; 55,95</t>
+          <t>11,74; 54,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 20,6</t>
+          <t>-55,16; 20,51</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 10,33</t>
+          <t>1,42; 10,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 12,21</t>
+          <t>2,78; 11,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,62</t>
+          <t>-1,26; 8,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 18,62</t>
+          <t>2,79; 17,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 54,43</t>
+          <t>6,16; 56,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,68; 58,25</t>
+          <t>10,49; 55,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 31,53</t>
+          <t>-3,83; 29,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,28; 272,05</t>
+          <t>13,74; 255,46</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,56</t>
+          <t>4,29; 8,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,05</t>
+          <t>3,26; 7,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,84</t>
+          <t>3,2; 7,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,45</t>
+          <t>-0,29; 10,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,09; 35,84</t>
+          <t>16,31; 36,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,85; 34,15</t>
+          <t>12,91; 32,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,38; 28,27</t>
+          <t>10,67; 27,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 49,22</t>
+          <t>-0,46; 46,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 10,39</t>
+          <t>-4,49; 10,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 9,36</t>
+          <t>-6,34; 8,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 11,58</t>
+          <t>-3,62; 12,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 10,49</t>
+          <t>-4,65; 10,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 61,05</t>
+          <t>-19,14; 57,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 44,18</t>
+          <t>-21,95; 36,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 44,64</t>
+          <t>-11,49; 45,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 32,4</t>
+          <t>-11,81; 33,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 12,13</t>
+          <t>0,02; 11,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 5,91</t>
+          <t>-4,64; 6,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 9,53</t>
+          <t>-1,71; 9,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 8,84</t>
+          <t>-3,04; 8,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 46,08</t>
+          <t>0,07; 46,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 27,21</t>
+          <t>-16,79; 30,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 37,85</t>
+          <t>-5,91; 37,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 44,79</t>
+          <t>-10,49; 42,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,97</t>
+          <t>9,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 12,58</t>
+          <t>-1,26; 12,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 19,05</t>
+          <t>5,91; 20,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 8,23</t>
+          <t>-5,28; 8,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,48</t>
+          <t>3,73; 15,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 63,52</t>
+          <t>-4,74; 69,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 95,38</t>
+          <t>21,3; 102,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 31,65</t>
+          <t>-15,77; 33,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,33; 87,74</t>
+          <t>14,69; 88,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>6,86</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 12,94</t>
+          <t>-0,75; 13,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 5,13</t>
+          <t>-6,85; 6,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 14,53</t>
+          <t>-0,02; 13,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 15,89</t>
+          <t>-0,76; 15,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 56,65</t>
+          <t>-2,58; 55,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 21,86</t>
+          <t>-23,2; 28,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 55,08</t>
+          <t>-0,11; 48,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 44,7</t>
+          <t>-2,06; 48,75</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 3,81</t>
+          <t>-12,61; 5,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 21,9</t>
+          <t>3,35; 21,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 16,8</t>
+          <t>1,52; 17,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 11,19</t>
+          <t>0,15; 10,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 13,96</t>
+          <t>-35,01; 18,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,15; 146,26</t>
+          <t>13,01; 132,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 135,97</t>
+          <t>4,15; 134,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 124,74</t>
+          <t>-1,17; 128,65</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 21,45</t>
+          <t>7,04; 21,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 7,79</t>
+          <t>-8,6; 7,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 13,64</t>
+          <t>-2,5; 14,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 11,11</t>
+          <t>-1,74; 10,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,67; 132,79</t>
+          <t>29,48; 135,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 30,26</t>
+          <t>-24,25; 29,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 43,0</t>
+          <t>-6,31; 45,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 53,44</t>
+          <t>-6,54; 56,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,03</t>
+          <t>3,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-14,45%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 14,38</t>
+          <t>4,01; 14,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,57</t>
+          <t>4,11; 14,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 14,1</t>
+          <t>2,95; 14,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 6,83</t>
+          <t>-1,59; 9,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,46; 56,1</t>
+          <t>13,12; 56,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,56; 65,91</t>
+          <t>14,95; 70,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 54,9</t>
+          <t>9,82; 58,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,16; 20,51</t>
+          <t>-4,3; 29,63</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 10,44</t>
+          <t>1,86; 10,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 11,74</t>
+          <t>3,27; 12,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 8,16</t>
+          <t>-1,53; 8,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 17,52</t>
+          <t>0,29; 7,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,16; 56,65</t>
+          <t>7,35; 56,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,49; 55,06</t>
+          <t>12,77; 59,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 29,89</t>
+          <t>-4,65; 30,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,74; 255,46</t>
+          <t>1,49; 45,62</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,66</t>
+          <t>4,14; 8,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,68</t>
+          <t>3,25; 7,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,71</t>
+          <t>3,11; 7,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,18</t>
+          <t>2,68; 6,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,31; 36,05</t>
+          <t>15,76; 35,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,91; 32,61</t>
+          <t>12,91; 32,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,67; 27,87</t>
+          <t>10,24; 28,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 46,89</t>
+          <t>9,66; 28,26</t>
         </is>
       </c>
     </row>
